--- a/数学群_20261003.xlsx
+++ b/数学群_20261003.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qingg\Python\checkin\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B51EB58EE9636413537FED9977FF922688EF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B51EBE266D5064F34376EC9106F7F22688EF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,7 +428,7 @@
       <c r="A1" s="2"/>
       <c r="B1" s="2">
         <f>SUM(B3:B10000)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -633,10 +633,10 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -648,10 +648,10 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -843,10 +843,10 @@
       </c>
       <c r="B29" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="3">
         <v>2</v>
@@ -948,10 +948,10 @@
       </c>
       <c r="B36" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
@@ -1143,10 +1143,10 @@
       </c>
       <c r="B49" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="3">
         <v>2</v>
@@ -1173,10 +1173,10 @@
       </c>
       <c r="B51" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="3">
         <v>0</v>

--- a/数学群_20261003.xlsx
+++ b/数学群_20261003.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qingg\Python\checkin\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B51EBE266D5064F34376EC9106F7F22688EF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B51EB40A6D1345D3437377150449523688EF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,7 +428,7 @@
       <c r="A1" s="2"/>
       <c r="B1" s="2">
         <f>SUM(B3:B10000)</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -468,10 +468,10 @@
       </c>
       <c r="B4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
@@ -648,10 +648,10 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -1143,10 +1143,10 @@
       </c>
       <c r="B49" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="3">
         <v>2</v>

--- a/数学群_20261003.xlsx
+++ b/数学群_20261003.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qingg\Python\checkin\WeChatTextExport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B51EB40A6D1345D3437377150449523688EF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B3523C415C626353437905912587522688EE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -416,15 +416,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.9296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.9140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2">
         <f>SUM(B3:B10000)</f>
@@ -433,7 +433,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>29101</v>
       </c>
@@ -462,7 +462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>29102</v>
       </c>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>29103</v>
       </c>
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>29104</v>
       </c>
@@ -507,7 +507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>29105</v>
       </c>
@@ -522,7 +522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>29106</v>
       </c>
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>29107</v>
       </c>
@@ -552,7 +552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>29108</v>
       </c>
@@ -567,7 +567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>29109</v>
       </c>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>29110</v>
       </c>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>29111</v>
       </c>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>29112</v>
       </c>
@@ -627,7 +627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>29113</v>
       </c>
@@ -642,7 +642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>29114</v>
       </c>
@@ -657,7 +657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>29115</v>
       </c>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>29116</v>
       </c>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>29117</v>
       </c>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>29118</v>
       </c>
@@ -717,7 +717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>29151</v>
       </c>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>29152</v>
       </c>
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>29153</v>
       </c>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>29154</v>
       </c>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>29155</v>
       </c>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>29156</v>
       </c>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>29157</v>
       </c>
@@ -822,7 +822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>29158</v>
       </c>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>29159</v>
       </c>
@@ -852,7 +852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29160</v>
       </c>
@@ -867,7 +867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>29161</v>
       </c>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29162</v>
       </c>
@@ -897,7 +897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>29163</v>
       </c>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>29164</v>
       </c>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>29165</v>
       </c>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>29166</v>
       </c>
@@ -957,7 +957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>29167</v>
       </c>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>29168</v>
       </c>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>29169</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>29170</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>29171</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>29172</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>29173</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>29174</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>29175</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>29176</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>29177</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>29178</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>29179</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>29180</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>29181</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>29182</v>
       </c>

--- a/数学群_20261003.xlsx
+++ b/数学群_20261003.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B3523C415C626353437905912587522688EE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B352324C5C6279B343716A11777F322688EE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,7 +428,7 @@
       <c r="A1" s="2"/>
       <c r="B1" s="2">
         <f>SUM(B3:B10000)</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -483,10 +483,10 @@
       </c>
       <c r="B5" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
@@ -888,10 +888,10 @@
       </c>
       <c r="B32" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="3">
         <v>2</v>
